--- a/data/Supplementary_Tables.xlsx
+++ b/data/Supplementary_Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seung-hwan.kim/Desktop/Hybrid_OU_Branching_Pediatric_Leukemia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seung-hwan.kim/Desktop/Hybrid_OU_Branching_Pediatric_Leukemia/iScience/Revision/Revision Package/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7441C40-1B0A-9049-A1AB-635843C19075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84326CF-009E-6840-9A22-6DF151754F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4720" yWindow="-20980" windowWidth="33680" windowHeight="20320" activeTab="6" xr2:uid="{B09B8C7A-FE1C-7045-A7B8-1047EF4811E4}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="22940" windowHeight="13540" firstSheet="3" activeTab="7" xr2:uid="{B09B8C7A-FE1C-7045-A7B8-1047EF4811E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sim_Params" sheetId="4" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Simulation_Summary" sheetId="7" r:id="rId5"/>
     <sheet name="Patient_Outputs" sheetId="5" r:id="rId6"/>
     <sheet name="Lineage_Metrics_Summary" sheetId="6" r:id="rId7"/>
+    <sheet name="Case_Level_Model_Comparison" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="217">
   <si>
     <t>Patient_ID</t>
   </si>
@@ -749,6 +750,94 @@
       </rPr>
       <t xml:space="preserve"> Lineage metrics summary</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Supplementary Table S8:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Case-Level Model Comparison</t>
+    </r>
+  </si>
+  <si>
+    <t>Patient</t>
+  </si>
+  <si>
+    <t>n_timepoints</t>
+  </si>
+  <si>
+    <t>min_day</t>
+  </si>
+  <si>
+    <t>max_day</t>
+  </si>
+  <si>
+    <t>n_variants_median</t>
+  </si>
+  <si>
+    <t>mean_vaf_diagnosis</t>
+  </si>
+  <si>
+    <t>mean_vaf_final</t>
+  </si>
+  <si>
+    <t>Infant/Child</t>
+  </si>
+  <si>
+    <t>Survival</t>
+  </si>
+  <si>
+    <t>best_model</t>
+  </si>
+  <si>
+    <t>best_AICc</t>
+  </si>
+  <si>
+    <t>best_weight</t>
+  </si>
+  <si>
+    <t>delta_AICc_Brownian</t>
+  </si>
+  <si>
+    <t>delta_AICc_Branching-only drift</t>
+  </si>
+  <si>
+    <t>delta_AICc_OU</t>
+  </si>
+  <si>
+    <t>delta_AICc_Markov-emission</t>
+  </si>
+  <si>
+    <t>delta_AICc_OU-Branching jump</t>
+  </si>
+  <si>
+    <t>Infant</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>OU</t>
+  </si>
+  <si>
+    <t>Alive</t>
+  </si>
+  <si>
+    <t>OU-Branching jump</t>
   </si>
 </sst>
 </file>
@@ -10487,4 +10576,1073 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B47335-7320-034E-881D-E80532C250BF}">
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="O3" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="P3" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q3" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="R3" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="S3" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="T3" s="22" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="23">
+        <v>11</v>
+      </c>
+      <c r="C4" s="23">
+        <v>0</v>
+      </c>
+      <c r="D4" s="23">
+        <v>223</v>
+      </c>
+      <c r="E4" s="23">
+        <v>11</v>
+      </c>
+      <c r="F4" s="23">
+        <v>0.212847400334501</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0.26706810106349399</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="L4" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M4" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="N4" s="23">
+        <v>38.171131157687803</v>
+      </c>
+      <c r="O4" s="23">
+        <v>0.78754161004521495</v>
+      </c>
+      <c r="P4" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>3.2115867768830002</v>
+      </c>
+      <c r="R4" s="23">
+        <v>5.5358311379814999</v>
+      </c>
+      <c r="S4" s="23">
+        <v>10.233899765971699</v>
+      </c>
+      <c r="T4" s="23">
+        <v>16.533579043697799</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="23">
+        <v>12</v>
+      </c>
+      <c r="C5" s="23">
+        <v>0</v>
+      </c>
+      <c r="D5" s="23">
+        <v>287</v>
+      </c>
+      <c r="E5" s="23">
+        <v>12</v>
+      </c>
+      <c r="F5" s="23">
+        <v>0.421104123054932</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0.14460955574170201</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="N5" s="23">
+        <v>60.077663816376202</v>
+      </c>
+      <c r="O5" s="23">
+        <v>0.74705386561412002</v>
+      </c>
+      <c r="P5" s="23">
+        <v>3.1097358092864802</v>
+      </c>
+      <c r="Q5" s="23">
+        <v>6.1542071352465904</v>
+      </c>
+      <c r="R5" s="23">
+        <v>0</v>
+      </c>
+      <c r="S5" s="23">
+        <v>5.0660356480423197</v>
+      </c>
+      <c r="T5" s="23">
+        <v>12.571428585969</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="23">
+        <v>11</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0</v>
+      </c>
+      <c r="D6" s="23">
+        <v>341</v>
+      </c>
+      <c r="E6" s="23">
+        <v>12</v>
+      </c>
+      <c r="F6" s="23">
+        <v>0.40321046143200701</v>
+      </c>
+      <c r="G6" s="23">
+        <v>1.69652409642509E-3</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="N6" s="23">
+        <v>45.221215337481297</v>
+      </c>
+      <c r="O6" s="23">
+        <v>0.54606197298216497</v>
+      </c>
+      <c r="P6" s="23">
+        <v>1.79561047910149</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>4.36677539247236</v>
+      </c>
+      <c r="R6" s="23">
+        <v>0</v>
+      </c>
+      <c r="S6" s="23">
+        <v>8.2669386664962801</v>
+      </c>
+      <c r="T6" s="23">
+        <v>2.4405797229776098</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="23">
+        <v>15</v>
+      </c>
+      <c r="C7" s="23">
+        <v>0</v>
+      </c>
+      <c r="D7" s="23">
+        <v>575</v>
+      </c>
+      <c r="E7" s="23">
+        <v>35</v>
+      </c>
+      <c r="F7" s="23">
+        <v>7.0137481795880502E-2</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0.268908607737609</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="N7" s="23">
+        <v>54.830943931414701</v>
+      </c>
+      <c r="O7" s="23">
+        <v>0.42539232302867203</v>
+      </c>
+      <c r="P7" s="23">
+        <v>4.6530821729490399E-2</v>
+      </c>
+      <c r="Q7" s="23">
+        <v>2.7433504400521702</v>
+      </c>
+      <c r="R7" s="23">
+        <v>4.9918146127351397</v>
+      </c>
+      <c r="S7" s="23">
+        <v>6.5580617850959699</v>
+      </c>
+      <c r="T7" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="23">
+        <v>11</v>
+      </c>
+      <c r="C8" s="23">
+        <v>0</v>
+      </c>
+      <c r="D8" s="23">
+        <v>679</v>
+      </c>
+      <c r="E8" s="23">
+        <v>17</v>
+      </c>
+      <c r="F8" s="23">
+        <v>0.24432799713272901</v>
+      </c>
+      <c r="G8" s="23">
+        <v>1.0995791253507099E-3</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="N8" s="23">
+        <v>41.833855957787698</v>
+      </c>
+      <c r="O8" s="23">
+        <v>0.79385991975433601</v>
+      </c>
+      <c r="P8" s="23">
+        <v>7.7505302151417004</v>
+      </c>
+      <c r="Q8" s="23">
+        <v>10.7542615457028</v>
+      </c>
+      <c r="R8" s="23">
+        <v>0</v>
+      </c>
+      <c r="S8" s="23">
+        <v>9.2007869024500604</v>
+      </c>
+      <c r="T8" s="23">
+        <v>2.9899848896914598</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="23">
+        <v>9</v>
+      </c>
+      <c r="C9" s="23">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <v>132</v>
+      </c>
+      <c r="E9" s="23">
+        <v>10</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.23227599918311401</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.1973207998282</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="N9" s="23">
+        <v>39.571044267496099</v>
+      </c>
+      <c r="O9" s="23">
+        <v>0.97283580642592604</v>
+      </c>
+      <c r="P9" s="23">
+        <v>8.2159949798818896</v>
+      </c>
+      <c r="Q9" s="23">
+        <v>11.949038504836899</v>
+      </c>
+      <c r="R9" s="23">
+        <v>9.5046013957520508</v>
+      </c>
+      <c r="S9" s="23">
+        <v>16.174139699400602</v>
+      </c>
+      <c r="T9" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="23">
+        <v>9</v>
+      </c>
+      <c r="C10" s="23">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23">
+        <v>517</v>
+      </c>
+      <c r="E10" s="23">
+        <v>20</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.241079263318174</v>
+      </c>
+      <c r="G10" s="23">
+        <v>1.0746348509712701E-3</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="N10" s="23">
+        <v>42.369233582304702</v>
+      </c>
+      <c r="O10" s="23">
+        <v>0.76005182450959297</v>
+      </c>
+      <c r="P10" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="23">
+        <v>3.41198304083726</v>
+      </c>
+      <c r="R10" s="23">
+        <v>4.0273760581955003</v>
+      </c>
+      <c r="S10" s="23">
+        <v>14.797655206988001</v>
+      </c>
+      <c r="T10" s="23">
+        <v>32.027376175661097</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="23">
+        <v>13</v>
+      </c>
+      <c r="C11" s="23">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23">
+        <v>247</v>
+      </c>
+      <c r="E11" s="23">
+        <v>15</v>
+      </c>
+      <c r="F11" s="23">
+        <v>0.112874270561806</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0.40724650639964299</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="N11" s="23">
+        <v>28.261891448415</v>
+      </c>
+      <c r="O11" s="23">
+        <v>0.99990021403347595</v>
+      </c>
+      <c r="P11" s="23">
+        <v>19.0347046197118</v>
+      </c>
+      <c r="Q11" s="23">
+        <v>21.882035981133299</v>
+      </c>
+      <c r="R11" s="23">
+        <v>23.5481861505578</v>
+      </c>
+      <c r="S11" s="23">
+        <v>28.043120362336499</v>
+      </c>
+      <c r="T11" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="23">
+        <v>8</v>
+      </c>
+      <c r="C12" s="23">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
+        <v>736</v>
+      </c>
+      <c r="E12" s="23">
+        <v>6</v>
+      </c>
+      <c r="F12" s="23">
+        <v>0.24911068899535299</v>
+      </c>
+      <c r="G12" s="23">
+        <v>1.5564128645844E-3</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="N12" s="23">
+        <v>40.113851228938103</v>
+      </c>
+      <c r="O12" s="23">
+        <v>0.73457872191554596</v>
+      </c>
+      <c r="P12" s="23">
+        <v>2.28905300132925</v>
+      </c>
+      <c r="Q12" s="23">
+        <v>6.3372082942390202</v>
+      </c>
+      <c r="R12" s="23">
+        <v>0</v>
+      </c>
+      <c r="S12" s="23">
+        <v>14.054017905286999</v>
+      </c>
+      <c r="T12" s="23">
+        <v>53.5401293770527</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="23">
+        <v>10</v>
+      </c>
+      <c r="C13" s="23">
+        <v>21</v>
+      </c>
+      <c r="D13" s="23">
+        <v>2408</v>
+      </c>
+      <c r="E13" s="23">
+        <v>35</v>
+      </c>
+      <c r="F13" s="23">
+        <v>2.3469466950686E-2</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0.13745376525650099</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="N13" s="23">
+        <v>40.287893288842298</v>
+      </c>
+      <c r="O13" s="23">
+        <v>0.99904070434635095</v>
+      </c>
+      <c r="P13" s="23">
+        <v>15.609710281640901</v>
+      </c>
+      <c r="Q13" s="23">
+        <v>19.028318337953699</v>
+      </c>
+      <c r="R13" s="23">
+        <v>15.5280241235607</v>
+      </c>
+      <c r="S13" s="23">
+        <v>19.6560994254002</v>
+      </c>
+      <c r="T13" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="23">
+        <v>9</v>
+      </c>
+      <c r="C14" s="23">
+        <v>0</v>
+      </c>
+      <c r="D14" s="23">
+        <v>742</v>
+      </c>
+      <c r="E14" s="23">
+        <v>21</v>
+      </c>
+      <c r="F14" s="23">
+        <v>0.15705986945969699</v>
+      </c>
+      <c r="G14" s="23">
+        <v>2.8619239798831101E-3</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="N14" s="23">
+        <v>39.713975479992499</v>
+      </c>
+      <c r="O14" s="23">
+        <v>0.77205729863904904</v>
+      </c>
+      <c r="P14" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="23">
+        <v>3.5838230903575501</v>
+      </c>
+      <c r="R14" s="23">
+        <v>4.38687764826338</v>
+      </c>
+      <c r="S14" s="23">
+        <v>8.1412701448077307</v>
+      </c>
+      <c r="T14" s="23">
+        <v>30.512873138927102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A15" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="23">
+        <v>8</v>
+      </c>
+      <c r="C15" s="23">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1734</v>
+      </c>
+      <c r="E15" s="23">
+        <v>15</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0.28685823771908803</v>
+      </c>
+      <c r="G15" s="23">
+        <v>6.5419672701006197E-4</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="N15" s="23">
+        <v>16.119011957960002</v>
+      </c>
+      <c r="O15" s="23">
+        <v>0.96356894727918496</v>
+      </c>
+      <c r="P15" s="23">
+        <v>26.9226451207089</v>
+      </c>
+      <c r="Q15" s="23">
+        <v>30.930059144470999</v>
+      </c>
+      <c r="R15" s="23">
+        <v>0</v>
+      </c>
+      <c r="S15" s="23">
+        <v>6.5505306206801102</v>
+      </c>
+      <c r="T15" s="23">
+        <v>54.2513927535825</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A16" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="23">
+        <v>11</v>
+      </c>
+      <c r="C16" s="23">
+        <v>0</v>
+      </c>
+      <c r="D16" s="23">
+        <v>685</v>
+      </c>
+      <c r="E16" s="23">
+        <v>11</v>
+      </c>
+      <c r="F16" s="23">
+        <v>0.36773236910618801</v>
+      </c>
+      <c r="G16" s="23">
+        <v>1.67103602428826E-4</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="L16" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="M16" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="N16" s="23">
+        <v>47.856378689859</v>
+      </c>
+      <c r="O16" s="23">
+        <v>0.78838020788614505</v>
+      </c>
+      <c r="P16" s="23">
+        <v>14.707790907128301</v>
+      </c>
+      <c r="Q16" s="23">
+        <v>17.702400750485101</v>
+      </c>
+      <c r="R16" s="23">
+        <v>2.80135605018565</v>
+      </c>
+      <c r="S16" s="23">
+        <v>7.7065276239251403</v>
+      </c>
+      <c r="T16" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A17" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="23">
+        <v>18</v>
+      </c>
+      <c r="C17" s="23">
+        <v>0</v>
+      </c>
+      <c r="D17" s="23">
+        <v>546</v>
+      </c>
+      <c r="E17" s="23">
+        <v>13</v>
+      </c>
+      <c r="F17" s="23">
+        <v>0.18060929153358299</v>
+      </c>
+      <c r="G17" s="23">
+        <v>0.256906640027112</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="L17" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="N17" s="23">
+        <v>77.150895026737601</v>
+      </c>
+      <c r="O17" s="23">
+        <v>0.67480820812322895</v>
+      </c>
+      <c r="P17" s="23">
+        <v>18.304303345626501</v>
+      </c>
+      <c r="Q17" s="23">
+        <v>20.894262407362401</v>
+      </c>
+      <c r="R17" s="23">
+        <v>3.83904589094361</v>
+      </c>
+      <c r="S17" s="23">
+        <v>2.1867086585327198</v>
+      </c>
+      <c r="T17" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="23">
+        <v>10</v>
+      </c>
+      <c r="C18" s="23">
+        <v>0</v>
+      </c>
+      <c r="D18" s="23">
+        <v>460</v>
+      </c>
+      <c r="E18" s="23">
+        <v>16</v>
+      </c>
+      <c r="F18" s="23">
+        <v>0.18475990286931501</v>
+      </c>
+      <c r="G18" s="23">
+        <v>0.158394248109473</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="N18" s="23">
+        <v>50.9485656028438</v>
+      </c>
+      <c r="O18" s="23">
+        <v>0.579982643111702</v>
+      </c>
+      <c r="P18" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="23">
+        <v>3.42835040532636</v>
+      </c>
+      <c r="R18" s="23">
+        <v>1.54570346328996</v>
+      </c>
+      <c r="S18" s="23">
+        <v>5.0119654687039299</v>
+      </c>
+      <c r="T18" s="23">
+        <v>14.2935970734818</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="23">
+        <v>10</v>
+      </c>
+      <c r="C19" s="23">
+        <v>0</v>
+      </c>
+      <c r="D19" s="23">
+        <v>815</v>
+      </c>
+      <c r="E19" s="23">
+        <v>12</v>
+      </c>
+      <c r="F19" s="23">
+        <v>0.38512816275876599</v>
+      </c>
+      <c r="G19" s="23">
+        <v>3.3640745381474301E-3</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="L19" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="N19" s="23">
+        <v>49.049795795838897</v>
+      </c>
+      <c r="O19" s="23">
+        <v>0.89795298583285099</v>
+      </c>
+      <c r="P19" s="23">
+        <v>7.2298332990553096</v>
+      </c>
+      <c r="Q19" s="23">
+        <v>10.567164851089901</v>
+      </c>
+      <c r="R19" s="23">
+        <v>0</v>
+      </c>
+      <c r="S19" s="23">
+        <v>5.6999374413685997</v>
+      </c>
+      <c r="T19" s="23">
+        <v>7.4757586846035498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>